--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -657,19 +657,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -774,11 +774,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX4"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -1148,10 +1148,8 @@
           <t>Tek Raj Bhattarai</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9861431231</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9861431231</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1186,10 +1184,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.672145</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.672145</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -1245,25 +1241,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>3,13</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.282233</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.28223300000001</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : only one light in router   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1364,10 +1356,8 @@
           <t>Krishna kumar basnet</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9849335487</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9849335487</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1457,10 +1447,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1471,7 +1459,7 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
@@ -1572,10 +1560,8 @@
           <t>Kanchhi Tamang</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9843863828</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9843863828</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1610,10 +1596,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.656438</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.656438</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1665,53 +1649,481 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>L53-2</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.374787</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.374787</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>20h 49m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>20h 49m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>20h 49m</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>20h 49m</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV4" s="3" t="inlineStr">
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 9:47 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : only one light in router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>only one light in router</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343214</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Tek Raj Bhattarai</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Tek Raj Bhattarai</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9861431231</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 08:04:03 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9861431231</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 07:30:34 AM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 09:47:24 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.672145</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Panga Near Panga Secondary School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>9848851796||bhattarairaj685@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>10:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.282233</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : only one light in router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 43m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 16m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : only one light in router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:00 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AW4" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343660</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Kanchhi Tamang</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Kanchhi Tamang</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9843863828</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:00:43 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9843863828</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:18:01 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:00:43 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.656438</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Near Sirutar khadhka gau,Bhaktapur Municipality, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>tamangrayal51@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>07:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>L53-2</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.374787</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>21h 42m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX4" s="3" t="inlineStr">
+      <c r="AX6" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
@@ -820,7 +820,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1764,10 +1764,8 @@
           <t>Tek Raj Bhattarai</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9861431231</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9861431231</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1802,10 +1800,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.672145</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.672145</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1861,25 +1857,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>3,13</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.282233</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.28223300000001</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : only one light in router   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -1980,10 +1972,8 @@
           <t>Kanchhi Tamang</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9843863828</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9843863828</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -2018,10 +2008,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.656438</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.656438</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -2077,25 +2065,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>L53-2</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.374787</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.374787</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -546,36 +546,72 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C4" s="4" t="n">
+      <c r="B6" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>80.0%</t>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -634,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -669,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -684,13 +720,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -706,10 +744,20 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -718,49 +766,111 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="6" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="6" t="n">
-        <v>1</v>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>3</v>
+      <c r="E6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -774,7 +884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX6"/>
+  <dimension ref="A1:AX9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -788,7 +898,7 @@
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
@@ -803,27 +913,27 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="40" customWidth="1" min="32" max="32"/>
-    <col width="30" customWidth="1" min="33" max="33"/>
+    <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="32" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
     <col width="23" customWidth="1" min="50" max="50"/>
@@ -2113,6 +2223,642 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:18 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>slow internet</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343646</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Manik lal Yadav</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Manik lal Yadav</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9813427907</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 09:23:55 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>LTP9813427907</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:09:16 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:18:34 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Tikathali , Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>test123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>CDB472</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>54m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>22h 9m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:31 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343059</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9851322004</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:31:16 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9851322004</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:50:55 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:31:16 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.71579</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Sarveshwor Mahadev Temple, Nayabasti, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Rita Singh</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L31-6</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.36397</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1d 13h 40m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:25 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Res light in stb  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Res light in stb</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343880</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Avishek Satyal</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Avishek Satyal</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9843171373</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:25:13 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9843171373</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:04:09 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:25:13 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.74341</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Maharajganj Near Banglamukhi Temple, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr"/>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L17-2</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.33884</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Res light in stb  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>19h 21m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Res light in stb  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -670,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>30.0%</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -779,10 +779,10 @@
         <v>1</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -832,45 +832,67 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>6</v>
+      <c r="E7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -884,7 +906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX9"/>
+  <dimension ref="A1:AX11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2290,10 +2312,8 @@
           <t>Manik lal Yadav</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9813427907</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9813427907</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -2328,10 +2348,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -2383,25 +2401,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>CDB472</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -2502,10 +2516,8 @@
           <t>Saradha Panta</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9851322004</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9851322004</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2540,10 +2552,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.71579</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.71579</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2595,25 +2605,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>L31-6</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.36397</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.36396999999999</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2714,10 +2720,8 @@
           <t>Avishek Satyal</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9843171373</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9843171373</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2752,10 +2756,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.74341</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.74341</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2789,10 +2791,8 @@
           <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="AH9" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH9" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI9" s="3" t="inlineStr"/>
       <c r="AJ9" s="3" t="inlineStr"/>
@@ -2807,55 +2807,479 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>L17-2</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.33884</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.33884</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>19h 21m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
           <t>Case : Res light in stb  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS9" s="3" t="inlineStr">
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:43 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>slow internet</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343489</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Indra rai</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Indra rai</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9862062974</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:41:41 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>BKT9862062974</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:43:55 AM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:43:45 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Nrw thimi, Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>Test@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>22h 2m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>23h 59m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:41 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : No light on router   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>No light on router</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344041</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Milan Suwal</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Milan Suwal</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9843304328</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:41:54 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9843304328</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 05:16:21 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:41:54 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.670306</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Khwopa Engineering College, Libali-2, Bhaktapur 44800, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>mee.lone28@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>03:25 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Adhikari</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L17-3</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.439137</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : No light on router   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>19h 21m</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV9" s="3" t="inlineStr">
-        <is>
-          <t>Case : Res light in stb  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW9" s="3" t="inlineStr">
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>17h 25m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : No light on router   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX9" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>5</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -693,19 +693,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>1</v>
@@ -892,7 +892,7 @@
         <v>4</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -906,7 +906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX11"/>
+  <dimension ref="A1:AX12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2922,10 +2922,8 @@
           <t>Indra rai</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9862062974</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9862062974</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2960,10 +2958,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -3015,25 +3011,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>2,7</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -3134,10 +3126,8 @@
           <t>Milan Suwal</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9843304328</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9843304328</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -3172,10 +3162,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.670306</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.670306</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -3231,47 +3219,43 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>L17-3</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.439137</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.439137</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>17h 25m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
           <t>Case : No light on router   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS11" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT11" s="3" t="inlineStr">
-        <is>
-          <t>17h 25m</t>
-        </is>
-      </c>
-      <c r="AU11" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV11" s="3" t="inlineStr">
-        <is>
-          <t>Case : No light on router   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW11" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -3280,6 +3264,210 @@
       <c r="AX11" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:48 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343458</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Nigam Bakhariya</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Nigam Bakhariya</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9869216939</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:29:33 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9869216939</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:29:33 AM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:48:31 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr"/>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>M7CH+6J8 Kirtipur 44600,NEAR Panga Bus Park, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>nigambakhariya123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr"/>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr"/>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>1d 18m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 18m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
@@ -952,7 +952,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3334,10 +3334,8 @@
           <t>Nigam Bakhariya</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9869216939</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9869216939</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3423,10 +3421,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
@@ -3437,7 +3433,7 @@
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -693,19 +693,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -776,19 +776,19 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -798,10 +798,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>3</v>
@@ -889,10 +889,10 @@
         <v>2</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -906,7 +906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX12"/>
+  <dimension ref="A1:AX15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -952,7 +952,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3467,6 +3467,650 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:51 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344159</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Bhishma Uprety</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Bhishma Uprety</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9842788566</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:51:17 AM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9842788566</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 07:24:41 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:51:17 AM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.68512</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>near by Danphe Chari Marg Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>prabeshuprety1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>02:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.3314</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>16h 26m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:13 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344035</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Nikita Upadhaya</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Nikita Upadhaya</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9818106969</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 05:10:05 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9841865344</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 05:10:05 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:13:19 AM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.67843</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Near Advance oral dental hospital Saraswati Marga, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>neekitaupadhyay5@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.3465</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>18h 3m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>18h 3m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:08 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343797</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Anish Pradhan</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Anish Pradhan</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9860428234</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:08:35 AM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9860428234</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:09:53 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:08:35 AM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>27.672004</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>SallaGhari Near By Nepal Skin Bhaktapur,01, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>pradhananish4@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>06:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>2,9</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>85.409664</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>20h 58m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
@@ -952,7 +952,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3534,10 +3534,8 @@
           <t>Bhishma Uprety</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9842788566</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9842788566</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3572,10 +3570,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>27.68512</t>
-        </is>
+      <c r="Y13" s="3" t="n">
+        <v>27.68512</v>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
@@ -3631,25 +3627,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>1,5</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.3314</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.3314</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
@@ -3750,10 +3742,8 @@
           <t>Nikita Upadhaya</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9818106969</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9818106969</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3788,10 +3778,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.67843</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.67843</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -3843,25 +3831,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>1,4</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.3465</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.34650000000001</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3962,10 +3946,8 @@
           <t>Anish Pradhan</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9860428234</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9860428234</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -4000,10 +3982,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>27.672004</t>
-        </is>
+      <c r="Y15" s="3" t="n">
+        <v>27.672004</v>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
@@ -4059,25 +4039,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>2,9</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>85.409664</t>
-        </is>
+      <c r="AP15" s="3" t="n">
+        <v>85.40966400000001</v>
       </c>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -682,28 +682,51 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>6.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="B4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
@@ -720,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -776,13 +799,13 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>5</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -810,7 +833,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -820,10 +843,10 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>1</v>
@@ -832,7 +855,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -842,10 +865,10 @@
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>1</v>
@@ -854,45 +877,67 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>12</v>
+      <c r="D8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -906,7 +951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX15"/>
+  <dimension ref="A1:AX17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -952,7 +997,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4087,6 +4132,438 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:21 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344272</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Anil Aryal</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Anil Aryal</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9849610463</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:21:13 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>LTP9849610463</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 09:09:54 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:21:13 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Tikathali kharibot , Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>test123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>02:21 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Bashu Bhat</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>CDB472</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>15h 11m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:10 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344220</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Samir Subedi</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Samir Subedi</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9813870559</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:10:44 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9813870559</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 08:15:25 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:10:44 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>27.715676</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Kumari Bhairab Road Nayabasti, Gokarneshwor ward no:6,near Kumari Bhairab Temple , Bagmati, Central,</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr"/>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>02:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>L52-2</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>85.367613</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>15h 55m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
@@ -997,7 +997,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4199,10 +4199,8 @@
           <t>Anil Aryal</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9849610463</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9849610463</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -4237,10 +4235,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -4278,10 +4274,8 @@
           <t>NETTV-Blank TV Display</t>
         </is>
       </c>
-      <c r="AH16" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH16" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
@@ -4300,25 +4294,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>CDB472</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -4419,10 +4409,8 @@
           <t>Samir Subedi</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9813870559</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9813870559</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -4457,10 +4445,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>27.715676</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>27.715676</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -4512,25 +4498,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>L52-2</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>85.367613</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>85.36761300000001</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>58.8%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>41.2%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>5.9%</t>
         </is>
       </c>
     </row>
@@ -716,19 +716,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
     </row>
@@ -802,10 +802,10 @@
         <v>1</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -934,10 +934,10 @@
         <v>3</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -951,7 +951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX17"/>
+  <dimension ref="A1:AX18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -997,7 +997,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4546,6 +4546,210 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:55 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344169</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>sabin basnet</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>sabin basnet</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9803241299</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:55:27 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9863542185</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 07:33:00 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:55:27 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur	sankhamul, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr"/>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>03:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>4,16</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>17h 22m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
@@ -997,7 +997,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4613,10 +4613,8 @@
           <t>sabin basnet</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9803241299</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9803241299</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4702,10 +4700,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
@@ -4716,7 +4712,7 @@
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.1%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>5.6%</t>
         </is>
       </c>
     </row>
@@ -716,19 +716,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -799,13 +799,13 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>6</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -931,13 +931,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>9</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -951,7 +951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX18"/>
+  <dimension ref="A1:AX19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -997,7 +997,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4746,6 +4746,210 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 1:39 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344280</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Asad ul haq</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Asad ul haq</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9827815110</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 01:39:14 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9827815110</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 09:18:20 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 01:42:24 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Attarkhel Nmc chowk	, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr"/>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>03:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Binod Dhami</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>L44-6</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>3m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>16h 24m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
@@ -997,7 +997,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4813,10 +4813,8 @@
           <t>Asad ul haq</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9827815110</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9827815110</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4902,10 +4900,8 @@
           <t>Binod Dhami</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
@@ -4916,7 +4912,7 @@
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>63.2%</t>
         </is>
       </c>
     </row>
@@ -670,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>42.1%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.3%</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>52.6%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX19"/>
+  <dimension ref="A1:AX20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -997,7 +997,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4946,6 +4946,222 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 3:47 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Res light in stb  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Res light in stb</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343880</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Avishek Satyal</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Avishek Satyal</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9843171373</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:25:13 AM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9843171373</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:04:09 PM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 03:47:39 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>27.74341</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Maharajganj Near Banglamukhi Temple, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr"/>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>10:43 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>L17-2</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>85.33884</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Res light in stb  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>5h 22m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>1d 43m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Res light in stb  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
@@ -997,7 +997,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -5013,10 +5013,8 @@
           <t>Avishek Satyal</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9843171373</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9843171373</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -5051,10 +5049,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>27.74341</t>
-        </is>
+      <c r="Y20" s="3" t="n">
+        <v>27.74341</v>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
@@ -5088,10 +5084,8 @@
           <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="AH20" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH20" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
@@ -5110,25 +5104,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>L17-2</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>85.33884</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>85.33884</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : Res light in stb  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
     </row>
@@ -670,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>45.0%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.0%</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -833,14 +833,14 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
@@ -849,7 +849,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -877,7 +877,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -928,7 +928,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>4</v>
@@ -937,7 +937,7 @@
         <v>9</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -951,7 +951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX20"/>
+  <dimension ref="A1:AX21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -997,7 +997,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -5152,6 +5152,222 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 4:20 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case :  router lost    has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>router lost</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342385</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Seven Seas logistic</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Seven Seas logistic</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9851000248</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 04:20:04 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9851000248</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 12:49:56 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 04:20:04 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>27.727913</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Near to Presidential Business School,Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>management@7seahnepal.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>23:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>CDB454</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>85.324016</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case :  router lost    has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 30m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case :  router lost    has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Sep_2026.xlsx
@@ -997,7 +997,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -5219,10 +5219,8 @@
           <t>Seven Seas logistic</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9851000248</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9851000248</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -5257,10 +5255,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t>27.727913</t>
-        </is>
+      <c r="Y21" s="3" t="n">
+        <v>27.727913</v>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
@@ -5316,25 +5312,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>CDB454</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>85.324016</t>
-        </is>
+      <c r="AP21" s="3" t="n">
+        <v>85.324016</v>
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case :  router lost    has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
